--- a/Deliverables/BOM/DigiKey_BOMs/Touch_Board_LD_DigiKey.xlsx
+++ b/Deliverables/BOM/DigiKey_BOMs/Touch_Board_LD_DigiKey.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iftik\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\IbrahimHyder-ReverseEngineering\Deliverables\BOM\DigiKey_BOMs\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F564A7-48CC-4DE6-B06C-BA1B28B969C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Touch_Board 1" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Touch_Board 1'!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="99">
   <si>
     <t>Description</t>
   </si>
@@ -255,9 +256,6 @@
   </si>
   <si>
     <t>CONN HEADER VERT 3POS 2.54MM</t>
-  </si>
-  <si>
-    <t>HDR1X3</t>
   </si>
   <si>
     <t>P7'P8</t>
@@ -325,19 +323,22 @@
     <t>Mouser</t>
   </si>
   <si>
-    <t xml:space="preserve">Ye part NON Stock han </t>
+    <t>Do not Mount</t>
+  </si>
+  <si>
+    <t>Part out of Stock</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -420,8 +421,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -440,8 +458,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="25">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -759,12 +783,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -803,24 +855,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -831,15 +865,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -923,9 +948,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -942,9 +964,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -952,9 +971,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -980,9 +996,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1008,13 +1021,93 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1295,7 +1388,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1327,31 +1420,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19"/>
-      <c r="W1" s="19"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
+      <c r="M1" s="82"/>
+      <c r="N1" s="82"/>
+      <c r="O1" s="82"/>
+      <c r="P1" s="82"/>
+      <c r="Q1" s="82"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="82"/>
+      <c r="T1" s="82"/>
+      <c r="U1" s="82"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="82"/>
     </row>
     <row r="2" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1428,77 +1521,77 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="I3" s="37" t="s">
+      <c r="H3" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="39">
+      <c r="J3" s="30">
         <v>3</v>
       </c>
-      <c r="K3" s="39">
+      <c r="K3" s="30">
         <f>J3*5</f>
         <v>15</v>
       </c>
-      <c r="L3" s="39">
+      <c r="L3" s="30">
         <f>J3*1000</f>
         <v>3000</v>
       </c>
-      <c r="M3" s="39">
+      <c r="M3" s="30">
         <f>J3*5000</f>
         <v>15000</v>
       </c>
-      <c r="N3" s="80" t="s">
+      <c r="N3" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="40">
+      <c r="O3" s="31">
         <v>0.12</v>
       </c>
-      <c r="P3" s="41">
+      <c r="P3" s="32">
         <f>O3*J3</f>
         <v>0.36</v>
       </c>
-      <c r="Q3" s="40">
+      <c r="Q3" s="31">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="R3" s="41">
+      <c r="R3" s="32">
         <f>Q3*K3</f>
         <v>1.26</v>
       </c>
-      <c r="S3" s="40">
+      <c r="S3" s="31">
         <v>2.2880000000000001E-2</v>
       </c>
-      <c r="T3" s="41">
+      <c r="T3" s="32">
         <f>S3*L3</f>
         <v>68.64</v>
       </c>
-      <c r="U3" s="42">
+      <c r="U3" s="33">
         <v>2.0160000000000001E-2</v>
       </c>
-      <c r="V3" s="41">
+      <c r="V3" s="32">
         <f>U3*M3</f>
         <v>302.40000000000003</v>
       </c>
-      <c r="W3" s="81"/>
+      <c r="W3" s="68"/>
       <c r="X3"/>
       <c r="Y3"/>
       <c r="Z3"/>
@@ -1522,158 +1615,158 @@
         <f>A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="43" t="s">
+      <c r="B4" s="84"/>
+      <c r="C4" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="I4" s="24" t="s">
+      <c r="H4" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="I4" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="J4" s="25">
+      <c r="J4" s="19">
         <v>1</v>
       </c>
-      <c r="K4" s="32">
+      <c r="K4" s="23">
         <f t="shared" ref="K4:K14" si="0">J4*5</f>
         <v>5</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="23">
         <f>J4*1000</f>
         <v>1000</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="23">
         <f>J4*5000</f>
         <v>5000</v>
       </c>
-      <c r="N4" s="35" t="s">
+      <c r="N4" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="22">
         <v>0.12</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="24">
         <f>O4*J4</f>
         <v>0.12</v>
       </c>
-      <c r="Q4" s="31">
+      <c r="Q4" s="22">
         <v>0.12</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="24">
         <f>Q4*K4</f>
         <v>0.6</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="22">
         <v>2.3519999999999999E-2</v>
       </c>
-      <c r="T4" s="33">
+      <c r="T4" s="24">
         <f>S4*L4</f>
         <v>23.52</v>
       </c>
-      <c r="U4" s="31">
+      <c r="U4" s="22">
         <v>1.864E-2</v>
       </c>
-      <c r="V4" s="34">
+      <c r="V4" s="25">
         <f>U4*M4</f>
         <v>93.2</v>
       </c>
-      <c r="W4" s="82"/>
+      <c r="W4" s="69"/>
     </row>
-    <row r="5" spans="1:40" s="23" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:40" s="17" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59" t="s">
+      <c r="B5" s="85"/>
+      <c r="C5" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="60" t="s">
+      <c r="D5" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="60" t="s">
+      <c r="E5" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="60" t="s">
+      <c r="F5" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="60" t="s">
+      <c r="G5" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="I5" s="60" t="s">
+      <c r="H5" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="38">
         <v>6</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="39">
         <f>J5*5</f>
         <v>30</v>
       </c>
-      <c r="L5" s="48">
+      <c r="L5" s="39">
         <f>J5*1000</f>
         <v>6000</v>
       </c>
-      <c r="M5" s="48">
+      <c r="M5" s="39">
         <f>J5*5000</f>
         <v>30000</v>
       </c>
-      <c r="N5" s="83" t="s">
+      <c r="N5" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="O5" s="61">
+      <c r="O5" s="51">
         <v>0.11</v>
       </c>
-      <c r="P5" s="62">
+      <c r="P5" s="52">
         <f>O5*J5</f>
         <v>0.66</v>
       </c>
-      <c r="Q5" s="61">
+      <c r="Q5" s="51">
         <v>7.8E-2</v>
       </c>
-      <c r="R5" s="62">
+      <c r="R5" s="52">
         <f>Q5*K5</f>
         <v>2.34</v>
       </c>
-      <c r="S5" s="61">
+      <c r="S5" s="51">
         <v>1.7440000000000001E-2</v>
       </c>
-      <c r="T5" s="62">
+      <c r="T5" s="52">
         <f>S5*L5</f>
         <v>104.64</v>
       </c>
-      <c r="U5" s="61">
+      <c r="U5" s="51">
         <v>1.6584000000000002E-2</v>
       </c>
-      <c r="V5" s="63">
+      <c r="V5" s="53">
         <f>U5*M5</f>
         <v>497.52000000000004</v>
       </c>
-      <c r="W5" s="84"/>
+      <c r="W5" s="71"/>
     </row>
     <row r="6" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="64" t="s">
+      <c r="C6" s="54" t="s">
         <v>44</v>
       </c>
       <c r="D6" s="8" t="s">
@@ -1689,24 +1782,24 @@
         <v>48</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J6" s="10">
         <v>1</v>
       </c>
       <c r="K6" s="11">
-        <f t="shared" ref="K5:K13" si="1">J6*5</f>
+        <f t="shared" ref="K6:K13" si="1">J6*5</f>
         <v>5</v>
       </c>
       <c r="L6" s="11">
-        <f t="shared" ref="L5:L13" si="2">J6*1000</f>
+        <f t="shared" ref="L6:L13" si="2">J6*1000</f>
         <v>1000</v>
       </c>
       <c r="M6" s="11">
-        <f t="shared" ref="M5:M13" si="3">J6*5000</f>
+        <f t="shared" ref="M6:M13" si="3">J6*5000</f>
         <v>5000</v>
       </c>
       <c r="N6" s="12" t="s">
@@ -1740,233 +1833,233 @@
         <f t="shared" ref="V6:V12" si="7">U6*M6</f>
         <v>615</v>
       </c>
-      <c r="W6" s="85"/>
+      <c r="W6" s="72"/>
     </row>
     <row r="7" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E7" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="G7" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="H7" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="I7" s="37" t="s">
+      <c r="H7" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="I7" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="J7" s="39">
+      <c r="J7" s="30">
         <v>3</v>
       </c>
-      <c r="K7" s="66">
+      <c r="K7" s="55">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="55">
         <f t="shared" si="2"/>
         <v>3000</v>
       </c>
-      <c r="M7" s="66">
+      <c r="M7" s="55">
         <f t="shared" si="3"/>
         <v>15000</v>
       </c>
-      <c r="N7" s="86" t="s">
+      <c r="N7" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="O7" s="42">
+      <c r="O7" s="33">
         <v>0.1</v>
       </c>
-      <c r="P7" s="67">
+      <c r="P7" s="56">
         <f t="shared" si="4"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="Q7" s="42">
+      <c r="Q7" s="33">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="R7" s="67">
+      <c r="R7" s="56">
         <f t="shared" si="5"/>
         <v>0.63</v>
       </c>
-      <c r="S7" s="42">
+      <c r="S7" s="33">
         <v>6.5900000000000004E-3</v>
       </c>
-      <c r="T7" s="67">
+      <c r="T7" s="56">
         <f t="shared" si="6"/>
         <v>19.77</v>
       </c>
-      <c r="U7" s="42">
+      <c r="U7" s="33">
         <v>5.4400000000000004E-3</v>
       </c>
-      <c r="V7" s="68">
+      <c r="V7" s="57">
         <f t="shared" si="7"/>
         <v>81.600000000000009</v>
       </c>
-      <c r="W7" s="87"/>
+      <c r="W7" s="74"/>
     </row>
     <row r="8" spans="1:40" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="22">
+      <c r="A8" s="16">
         <v>6</v>
       </c>
-      <c r="B8" s="69"/>
-      <c r="C8" s="44" t="s">
+      <c r="B8" s="87"/>
+      <c r="C8" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="45" t="s">
+      <c r="D8" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="45" t="s">
+      <c r="E8" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="45" t="s">
+      <c r="F8" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="45" t="s">
+      <c r="G8" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="H8" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="I8" s="45" t="s">
+      <c r="H8" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="I8" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="J8" s="47">
+      <c r="J8" s="38">
         <v>7</v>
       </c>
-      <c r="K8" s="48">
+      <c r="K8" s="39">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="L8" s="48">
+      <c r="L8" s="39">
         <f t="shared" si="2"/>
         <v>7000</v>
       </c>
-      <c r="M8" s="48">
+      <c r="M8" s="39">
         <f t="shared" si="3"/>
         <v>35000</v>
       </c>
-      <c r="N8" s="83" t="s">
+      <c r="N8" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="O8" s="70">
+      <c r="O8" s="58">
         <v>0.1</v>
       </c>
-      <c r="P8" s="62">
+      <c r="P8" s="52">
         <f t="shared" si="4"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="Q8" s="70">
+      <c r="Q8" s="58">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="R8" s="62">
+      <c r="R8" s="52">
         <f t="shared" si="5"/>
         <v>0.76999999999999991</v>
       </c>
-      <c r="S8" s="70">
+      <c r="S8" s="58">
         <v>3.16E-3</v>
       </c>
-      <c r="T8" s="62">
+      <c r="T8" s="52">
         <f t="shared" si="6"/>
         <v>22.12</v>
       </c>
-      <c r="U8" s="61">
+      <c r="U8" s="51">
         <v>2.8400000000000001E-3</v>
       </c>
-      <c r="V8" s="63">
+      <c r="V8" s="53">
         <f t="shared" si="7"/>
         <v>99.4</v>
       </c>
-      <c r="W8" s="88"/>
+      <c r="W8" s="75"/>
     </row>
     <row r="9" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="88" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="50" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="F9" s="50" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="H9" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="51" t="s">
-        <v>85</v>
-      </c>
-      <c r="J9" s="52">
+      <c r="J9" s="43">
         <v>1</v>
       </c>
-      <c r="K9" s="53">
+      <c r="K9" s="44">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L9" s="53">
+      <c r="L9" s="44">
         <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="M9" s="53">
+      <c r="M9" s="44">
         <f t="shared" si="3"/>
         <v>5000</v>
       </c>
-      <c r="N9" s="54" t="s">
+      <c r="N9" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="O9" s="55">
+      <c r="O9" s="46">
         <v>0.86</v>
       </c>
-      <c r="P9" s="56">
+      <c r="P9" s="47">
         <f t="shared" si="4"/>
         <v>0.86</v>
       </c>
-      <c r="Q9" s="70">
+      <c r="Q9" s="58">
         <v>0.86</v>
       </c>
-      <c r="R9" s="56">
+      <c r="R9" s="47">
         <f t="shared" si="5"/>
         <v>4.3</v>
       </c>
-      <c r="S9" s="55">
+      <c r="S9" s="46">
         <v>0.72</v>
       </c>
-      <c r="T9" s="56">
+      <c r="T9" s="47">
         <f t="shared" si="6"/>
         <v>720</v>
       </c>
-      <c r="U9" s="55">
+      <c r="U9" s="46">
         <v>0.72</v>
       </c>
-      <c r="V9" s="57">
+      <c r="V9" s="48">
         <f t="shared" si="7"/>
         <v>3600</v>
       </c>
-      <c r="W9" s="93" t="s">
+      <c r="W9" s="106" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1974,75 +2067,75 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="71" t="s">
+      <c r="B10" s="88"/>
+      <c r="C10" s="59" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="72" t="s">
+      <c r="D10" s="60" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="72" t="s">
+      <c r="E10" s="60" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="72" t="s">
+      <c r="F10" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="G10" s="72" t="s">
+      <c r="G10" s="60" t="s">
         <v>74</v>
       </c>
-      <c r="H10" s="73" t="s">
-        <v>96</v>
-      </c>
-      <c r="I10" s="73" t="s">
-        <v>86</v>
-      </c>
-      <c r="J10" s="74">
+      <c r="H10" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="I10" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="J10" s="62">
         <v>1</v>
       </c>
-      <c r="K10" s="75">
+      <c r="K10" s="63">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L10" s="75">
+      <c r="L10" s="63">
         <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="M10" s="75">
+      <c r="M10" s="63">
         <f t="shared" si="3"/>
         <v>5000</v>
       </c>
-      <c r="N10" s="92" t="s">
-        <v>97</v>
-      </c>
-      <c r="O10" s="76">
+      <c r="N10" s="78" t="s">
+        <v>96</v>
+      </c>
+      <c r="O10" s="64">
         <v>0.66</v>
       </c>
-      <c r="P10" s="77">
+      <c r="P10" s="65">
         <f t="shared" si="4"/>
         <v>0.66</v>
       </c>
-      <c r="Q10" s="76">
+      <c r="Q10" s="64">
         <v>0.66</v>
       </c>
-      <c r="R10" s="77">
+      <c r="R10" s="65">
         <f t="shared" si="5"/>
         <v>3.3000000000000003</v>
       </c>
-      <c r="S10" s="76">
+      <c r="S10" s="64">
         <v>0.28000000000000003</v>
       </c>
-      <c r="T10" s="77">
+      <c r="T10" s="65">
         <f t="shared" si="6"/>
         <v>280</v>
       </c>
-      <c r="U10" s="76">
+      <c r="U10" s="64">
         <v>0.252</v>
       </c>
-      <c r="V10" s="78">
+      <c r="V10" s="66">
         <f t="shared" si="7"/>
         <v>1260</v>
       </c>
-      <c r="W10" s="93" t="s">
+      <c r="W10" s="106" t="s">
         <v>98</v>
       </c>
     </row>
@@ -2050,299 +2143,303 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="79" t="s">
+      <c r="B11" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="37" t="s">
+      <c r="D11" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="F11" s="37">
+      <c r="E11" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="28">
         <v>61300311121</v>
       </c>
-      <c r="G11" s="37" t="s">
+      <c r="G11" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="I11" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="J11" s="39">
+      <c r="H11" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="I11" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="J11" s="30">
         <v>2</v>
       </c>
-      <c r="K11" s="66">
+      <c r="K11" s="55">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L11" s="66">
+      <c r="L11" s="55">
         <f t="shared" si="2"/>
         <v>2000</v>
       </c>
-      <c r="M11" s="66">
+      <c r="M11" s="55">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
-      <c r="N11" s="86" t="s">
+      <c r="N11" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="O11" s="42">
+      <c r="O11" s="33">
         <v>0.13</v>
       </c>
-      <c r="P11" s="67">
+      <c r="P11" s="56">
         <f t="shared" si="4"/>
         <v>0.26</v>
       </c>
-      <c r="Q11" s="42">
+      <c r="Q11" s="33">
         <v>0.106</v>
       </c>
-      <c r="R11" s="67">
+      <c r="R11" s="56">
         <f t="shared" si="5"/>
         <v>1.06</v>
       </c>
-      <c r="S11" s="42">
+      <c r="S11" s="33">
         <v>6.2399999999999997E-2</v>
       </c>
-      <c r="T11" s="67">
+      <c r="T11" s="56">
         <f t="shared" si="6"/>
         <v>124.8</v>
       </c>
-      <c r="U11" s="42">
+      <c r="U11" s="33">
         <v>6.2399999999999997E-2</v>
       </c>
-      <c r="V11" s="68">
+      <c r="V11" s="57">
         <f t="shared" si="7"/>
         <v>624</v>
       </c>
-      <c r="W11" s="87"/>
+      <c r="W11" s="74"/>
     </row>
     <row r="12" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="89" t="s">
+      <c r="B12" s="90"/>
+      <c r="C12" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="90" t="s">
+      <c r="E12" s="77" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="77" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="90" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="90" t="s">
+      <c r="G12" s="77" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="90" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="I12" s="30"/>
-      <c r="J12" s="25">
+      <c r="H12" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="I12" s="21"/>
+      <c r="J12" s="19">
         <v>1</v>
       </c>
-      <c r="K12" s="32">
+      <c r="K12" s="23">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L12" s="32">
+      <c r="L12" s="23">
         <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="M12" s="32">
+      <c r="M12" s="23">
         <f t="shared" si="3"/>
         <v>5000</v>
       </c>
-      <c r="N12" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="O12" s="31">
+      <c r="N12" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="O12" s="22">
         <v>1.2</v>
       </c>
-      <c r="P12" s="33">
+      <c r="P12" s="24">
         <f t="shared" si="4"/>
         <v>1.2</v>
       </c>
-      <c r="Q12" s="31">
+      <c r="Q12" s="22">
         <v>1</v>
       </c>
-      <c r="R12" s="33">
+      <c r="R12" s="24">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="S12" s="31">
+      <c r="S12" s="22">
         <v>0.7</v>
       </c>
-      <c r="T12" s="33">
+      <c r="T12" s="24">
         <f t="shared" si="6"/>
         <v>700</v>
       </c>
-      <c r="U12" s="31">
+      <c r="U12" s="22">
         <v>0.6</v>
       </c>
-      <c r="V12" s="34">
+      <c r="V12" s="25">
         <f t="shared" si="7"/>
         <v>3000</v>
       </c>
-      <c r="W12" s="82"/>
+      <c r="W12" s="69"/>
     </row>
     <row r="13" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="43" t="s">
+      <c r="B13" s="90"/>
+      <c r="C13" s="93" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="94" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="E13" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="G13" s="24" t="s">
+      <c r="F13" s="94" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" s="94" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="I13" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="J13" s="25">
+      <c r="H13" s="95" t="s">
+        <v>94</v>
+      </c>
+      <c r="I13" s="95" t="s">
+        <v>85</v>
+      </c>
+      <c r="J13" s="96">
         <v>6</v>
       </c>
-      <c r="K13" s="32">
+      <c r="K13" s="97">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="L13" s="32">
+      <c r="L13" s="97">
         <f t="shared" si="2"/>
         <v>6000</v>
       </c>
-      <c r="M13" s="32">
+      <c r="M13" s="97">
         <f t="shared" si="3"/>
         <v>30000</v>
       </c>
-      <c r="N13" s="30" t="s">
+      <c r="N13" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="O13" s="30" t="s">
+      <c r="O13" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="P13" s="30" t="s">
+      <c r="P13" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="Q13" s="30" t="s">
+      <c r="Q13" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="R13" s="30" t="s">
+      <c r="R13" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="S13" s="30" t="s">
+      <c r="S13" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="T13" s="30" t="s">
+      <c r="T13" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="U13" s="30" t="s">
+      <c r="U13" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="V13" s="30" t="s">
+      <c r="V13" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="W13" s="82"/>
+      <c r="W13" s="105" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="14" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
+      <c r="A14" s="92">
         <v>12</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="44" t="s">
+      <c r="B14" s="91"/>
+      <c r="C14" s="98" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="45" t="s">
+      <c r="E14" s="100" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="99" t="s">
         <v>82</v>
       </c>
-      <c r="E14" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="G14" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="H14" s="46" t="s">
-        <v>95</v>
-      </c>
-      <c r="I14" s="46" t="s">
-        <v>86</v>
-      </c>
-      <c r="J14" s="47">
+      <c r="G14" s="99" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" s="99" t="s">
+        <v>94</v>
+      </c>
+      <c r="I14" s="101" t="s">
+        <v>85</v>
+      </c>
+      <c r="J14" s="102">
         <v>2</v>
       </c>
-      <c r="K14" s="48">
+      <c r="K14" s="103">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="103">
         <f>J14*1000</f>
         <v>2000</v>
       </c>
-      <c r="M14" s="48">
+      <c r="M14" s="103">
         <f>J14*5000</f>
         <v>10000</v>
       </c>
-      <c r="N14" s="46" t="s">
+      <c r="N14" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="O14" s="46" t="s">
+      <c r="O14" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="P14" s="46" t="s">
+      <c r="P14" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="Q14" s="46" t="s">
+      <c r="Q14" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="R14" s="46" t="s">
+      <c r="R14" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="S14" s="46" t="s">
+      <c r="S14" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="T14" s="46" t="s">
+      <c r="T14" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="U14" s="46" t="s">
+      <c r="U14" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="V14" s="46" t="s">
+      <c r="V14" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="W14" s="91"/>
+      <c r="W14" s="104" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="15" spans="1:40" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J15" s="16" t="s">
+      <c r="J15" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
+      <c r="K15" s="79"/>
+      <c r="L15" s="79"/>
+      <c r="M15" s="79"/>
+      <c r="N15" s="79"/>
+      <c r="O15" s="79"/>
       <c r="R15" s="3">
         <f>SUM(R3:R4)</f>
         <v>1.8599999999999999</v>
@@ -2358,14 +2455,14 @@
       </c>
     </row>
     <row r="16" spans="1:40" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="J16" s="17" t="s">
+      <c r="J16" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
+      <c r="K16" s="80"/>
+      <c r="L16" s="80"/>
+      <c r="M16" s="80"/>
+      <c r="N16" s="80"/>
+      <c r="O16" s="80"/>
       <c r="P16" s="2">
         <f>SUM(P3:P4)</f>
         <v>0.48</v>
@@ -2467,16 +2564,16 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N3" r:id="rId1"/>
-    <hyperlink ref="N5" r:id="rId2"/>
-    <hyperlink ref="N6" r:id="rId3"/>
-    <hyperlink ref="N7" r:id="rId4"/>
-    <hyperlink ref="N8" r:id="rId5"/>
-    <hyperlink ref="N11" r:id="rId6"/>
-    <hyperlink ref="N12" r:id="rId7"/>
-    <hyperlink ref="N4" r:id="rId8"/>
-    <hyperlink ref="N9" r:id="rId9"/>
-    <hyperlink ref="N10" r:id="rId10"/>
+    <hyperlink ref="N3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="N7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="N8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N11" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N12" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N4" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N9" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N10" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.30555555555555558" bottom="0.30555555555555558" header="0" footer="0"/>
